--- a/04_DESIGN_TABLES/DesignTable_5504.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_5504.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O30"/>
+  <dimension ref="A1:P30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -541,6 +541,11 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -1829,24 +1834,50 @@
           <t>5504-06-04-FG</t>
         </is>
       </c>
+      <c r="B25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.54</v>
+      </c>
       <c r="I25" t="inlineStr">
         <is>
           <t>5504-06-04-FG</t>
         </is>
       </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>3/8-18 x 1/4-18 NPTF (female x female)</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5504-06-04 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5504-06-04 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): N1_1@DRIVE: Brennan TFA catalog p.32 table TFA-p032-t02 "5504-FG FP-FP 90 DEG ELBOW" row 5504-06-04-FG col "N LGTH" = "1.020" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 405.7, page verified True) [Brennan = yes 2026-10-18] - A1 female port face (column mapping: REPORT.md, table 5504); N1_2@DRIVE: Brennan TFA catalog p.32 table TFA-p032-t02 "5504-FG FP-FP 90 DEG ELBOW" row 5504-06-04-FG col "N1 LGTH" = "1.010" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 405.7, page verified True) [Brennan = yes 2026-10-18] - A2 female port face (column mapping: REPORT.md, table 5504); W@REF: Brennan TFA catalog p.32 table TFA-p032-t02 "5504-FG FP-FP 90 DEG ELBOW" row 5504-06-04-FG col "Y FLATS" = "0.875" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 405.7, page verified True) [Brennan = yes 2026-10-18] - forged body flats (column mapping: REPORT.md, table 5504); TAPDRILL1@BORE: end library: tap drill of the -06 female NPTF port = 0.57 (gen_straight2 FPT[6] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A; = Air-Way's per-size tap drill of OPEN_QUESTIONS A1) [Q-NEW-F1A-5504TAP = A1 answered YES 2026-10-18 (00_DOCS/ANSWERS_2026-10-18.md): Air-Way per-size tap drill on existing families]; TAPDRILL2@BORE: end library: tap drill of the -04 female NPTF port = 0.43 (gen_straight2 FPT[4] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A; = Air-Way's per-size tap drill of OPEN_QUESTIONS A1) [Q-NEW-F1A-5504TAP = A1 answered YES 2026-10-18 (00_DOCS/ANSWERS_2026-10-18.md): Air-Way per-size tap drill on existing families]; THDMAJ_A1@DRIVE: end library: pipe OD of the -06 NPTF thread = 0.675 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[6], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A2@DRIVE: end library: pipe OD of the -04 NPTF thread = 0.54 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[4], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Threads: thread callouts from the part number dashes in the format of the table's other rows; = Brennan TFA-p032-t02 thread columns (A1 NPTF 3/8-18, A2 NPTF 1/4-18) and OMi Items Side 1 / 2 / 3 Thread</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5504-06-04 dims are NOT assumed; confirm before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5504-06-04 dims are NOT assumed; confirm before modelling | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog, end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate)</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -1857,6 +1888,11 @@
       <c r="O25" t="inlineStr">
         <is>
           <t>5504-06-04-FG</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -1866,24 +1902,50 @@
           <t>5504-06-06-FG</t>
         </is>
       </c>
+      <c r="B26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.675</v>
+      </c>
       <c r="I26" t="inlineStr">
         <is>
           <t>5504-06-06-FG</t>
         </is>
       </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>3/8-18 x 3/8-18 NPTF (female x female)</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5504-06-06 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5504-06-06 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): N1_1@DRIVE: Brennan TFA catalog p.32 table TFA-p032-t02 "5504-FG FP-FP 90 DEG ELBOW" row 5504-06-06-FG col "N LGTH" = "1.020" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 415.8, page verified True) [Brennan = yes 2026-10-18] - A1 female port face (column mapping: REPORT.md, table 5504); N1_2@DRIVE: Brennan TFA catalog p.32 table TFA-p032-t02 "5504-FG FP-FP 90 DEG ELBOW" row 5504-06-06-FG col "N1 LGTH" = "1.020" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 415.8, page verified True) [Brennan = yes 2026-10-18] - A2 female port face (column mapping: REPORT.md, table 5504); W@REF: Brennan TFA catalog p.32 table TFA-p032-t02 "5504-FG FP-FP 90 DEG ELBOW" row 5504-06-06-FG col "Y FLATS" = "0.875" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 415.8, page verified True) [Brennan = yes 2026-10-18] - forged body flats (column mapping: REPORT.md, table 5504); TAPDRILL1@BORE: end library: tap drill of the -06 female NPTF port = 0.57 (gen_straight2 FPT[6] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A; = Air-Way's per-size tap drill of OPEN_QUESTIONS A1) [Q-NEW-F1A-5504TAP = A1 answered YES 2026-10-18 (00_DOCS/ANSWERS_2026-10-18.md): Air-Way per-size tap drill on existing families]; TAPDRILL2@BORE: end library: tap drill of the -06 female NPTF port = 0.57 (gen_straight2 FPT[6] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A; = Air-Way's per-size tap drill of OPEN_QUESTIONS A1) [Q-NEW-F1A-5504TAP = A1 answered YES 2026-10-18 (00_DOCS/ANSWERS_2026-10-18.md): Air-Way per-size tap drill on existing families]; THDMAJ_A1@DRIVE: end library: pipe OD of the -06 NPTF thread = 0.675 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[6], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A2@DRIVE: end library: pipe OD of the -06 NPTF thread = 0.675 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[6], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Threads: thread callouts from the part number dashes in the format of the table's other rows; = Brennan TFA-p032-t02 thread columns (A1 NPTF 3/8-18, A2 NPTF 3/8-18) and OMi Items Side 1 / 2 / 3 Thread</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5504-06-06 dims are NOT assumed; confirm before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5504-06-06 dims are NOT assumed; confirm before modelling | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog, end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate)</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1894,6 +1956,11 @@
       <c r="O26" t="inlineStr">
         <is>
           <t>5504-06-06-FG</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -1903,24 +1970,50 @@
           <t>5504-08-06-FG</t>
         </is>
       </c>
+      <c r="B27" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.675</v>
+      </c>
       <c r="I27" t="inlineStr">
         <is>
           <t>5504-08-06-FG</t>
         </is>
       </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>1/2-14 x 3/8-18 NPTF (female x female)</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5504-08-06 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5504-08-06 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): N1_1@DRIVE: Brennan TFA catalog p.32 table TFA-p032-t02 "5504-FG FP-FP 90 DEG ELBOW" row 5504-08-06-FG col "N LGTH" = "1.230" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 436.0, page verified True) [Brennan = yes 2026-10-18] - A1 female port face (column mapping: REPORT.md, table 5504); N1_2@DRIVE: Brennan TFA catalog p.32 table TFA-p032-t02 "5504-FG FP-FP 90 DEG ELBOW" row 5504-08-06-FG col "N1 LGTH" = "1.010" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 436.0, page verified True) [Brennan = yes 2026-10-18] - A2 female port face (column mapping: REPORT.md, table 5504); W@REF: Brennan TFA catalog p.32 table TFA-p032-t02 "5504-FG FP-FP 90 DEG ELBOW" row 5504-08-06-FG col "Y FLATS" = "1.062" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 436.0, page verified True) [Brennan = yes 2026-10-18] - forged body flats (column mapping: REPORT.md, table 5504); TAPDRILL1@BORE: end library: tap drill of the -08 female NPTF port = 0.7 (gen_straight2 FPT[8] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A; = Air-Way's per-size tap drill of OPEN_QUESTIONS A1) [Q-NEW-F1A-5504TAP = A1 answered YES 2026-10-18 (00_DOCS/ANSWERS_2026-10-18.md): Air-Way per-size tap drill on existing families]; TAPDRILL2@BORE: end library: tap drill of the -06 female NPTF port = 0.57 (gen_straight2 FPT[6] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A; = Air-Way's per-size tap drill of OPEN_QUESTIONS A1) [Q-NEW-F1A-5504TAP = A1 answered YES 2026-10-18 (00_DOCS/ANSWERS_2026-10-18.md): Air-Way per-size tap drill on existing families]; THDMAJ_A1@DRIVE: end library: pipe OD of the -08 NPTF thread = 0.84 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[8], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A2@DRIVE: end library: pipe OD of the -06 NPTF thread = 0.675 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[6], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Threads: thread callouts from the part number dashes in the format of the table's other rows; = Brennan TFA-p032-t02 thread columns (A1 NPTF 1/2-14, A2 NPTF 3/8-18) and OMi Items Side 1 / 2 / 3 Thread</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5504-08-06 dims are NOT assumed; confirm before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5504-08-06 dims are NOT assumed; confirm before modelling | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog, end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate)</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -1931,6 +2024,11 @@
       <c r="O27" t="inlineStr">
         <is>
           <t>5504-08-06-FG</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -1940,24 +2038,50 @@
           <t>5504-20-20-FG</t>
         </is>
       </c>
+      <c r="B28" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.66</v>
+      </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>5504-20-20-FG</t>
         </is>
       </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>1 1/4-11 1/2 x 1 1/4-11 1/2 NPTF (female x female)</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5504-20-20 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 5504-20-20 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): N1_1@DRIVE: Brennan TFA catalog p.32 table TFA-p032-t02 "5504-FG FP-FP 90 DEG ELBOW" row 5504-20-20-FG col "N LGTH" = "1.70" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 536.8, page verified True) [Brennan = yes 2026-10-18] - A1 female port face (column mapping: REPORT.md, table 5504); N1_2@DRIVE: Brennan TFA catalog p.32 table TFA-p032-t02 "5504-FG FP-FP 90 DEG ELBOW" row 5504-20-20-FG col "N1 LGTH" = "1.70" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 536.8, page verified True) [Brennan = yes 2026-10-18] - A2 female port face (column mapping: REPORT.md, table 5504); W@REF: Brennan TFA catalog p.32 table TFA-p032-t02 "5504-FG FP-FP 90 DEG ELBOW" row 5504-20-20-FG col "Y FLATS" = "1.875" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 536.8, page verified True) [Brennan = yes 2026-10-18] - forged body flats (column mapping: REPORT.md, table 5504); TAPDRILL1@BORE: end library: tap drill of the -20 female NPTF port = 1.48 (gen_straight2 FPT[20] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A; = Air-Way's per-size tap drill of OPEN_QUESTIONS A1) [Q-NEW-F1A-5504TAP = A1 answered YES 2026-10-18 (00_DOCS/ANSWERS_2026-10-18.md): Air-Way per-size tap drill on existing families]; TAPDRILL2@BORE: end library: tap drill of the -20 female NPTF port = 1.48 (gen_straight2 FPT[20] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A; = Air-Way's per-size tap drill of OPEN_QUESTIONS A1) [Q-NEW-F1A-5504TAP = A1 answered YES 2026-10-18 (00_DOCS/ANSWERS_2026-10-18.md): Air-Way per-size tap drill on existing families]; THDMAJ_A1@DRIVE: end library: pipe OD of the -20 NPTF thread = 1.66 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[20], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A2@DRIVE: end library: pipe OD of the -20 NPTF thread = 1.66 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[20], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Threads: thread callouts from the part number dashes in the format of the table's other rows; = Brennan TFA-p032-t02 thread columns (A1 NPTF 1-1/4-11-1/2, A2 NPTF 1-1/4-11-1/2) and OMi Items Side 1 / 2 / 3 Thread</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5504-20-20 dims are NOT assumed; confirm before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 5504-20-20 dims are NOT assumed; confirm before modelling | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog, end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate)</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -1968,6 +2092,11 @@
       <c r="O28" t="inlineStr">
         <is>
           <t>5504-20-20-FG</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
